--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -82,172 +82,79 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ABAD</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>BENITO</t>
+    <t>NIEVES</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>YAHIR</t>
   </si>
   <si>
     <t>ANGEL FIDEL</t>
   </si>
   <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>JOSE ALEJANDRO</t>
   </si>
   <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
+    <t>CANDIDO</t>
   </si>
   <si>
     <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -752,19 +659,19 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>23</v>
       </c>
       <c r="G6">
-        <v>71.88</v>
+        <v>74.19</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -846,16 +753,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -869,16 +779,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.12</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -892,16 +805,19 @@
         <v>27</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>27</v>
       </c>
-      <c r="E4">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -915,16 +831,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -935,19 +854,22 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -961,16 +883,19 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>88.64</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1026,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1052,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>90.23999999999999</v>
+        <v>95.12</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1078,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1113,7 +1038,7 @@
         <v>92.31</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1124,19 +1049,19 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>71.88</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -1156,16 +1081,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G7">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,16 +1132,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920171</v>
+        <v>21330051920154</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1230,16 +1155,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920177</v>
+        <v>21330051920171</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1253,16 +1178,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920181</v>
+        <v>21330051920177</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1276,22 +1201,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920255</v>
+        <v>19330061430023</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1299,22 +1224,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920282</v>
+        <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1322,22 +1247,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920286</v>
+        <v>21330051920316</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1345,323 +1270,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920331</v>
+        <v>21330051920176</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330061430023</v>
+        <v>21330051920304</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920195</v>
+        <v>21330051920330</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920202</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920203</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920213</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920303</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920316</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920175</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920268</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920304</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920307</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920330</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -97,15 +97,15 @@
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
@@ -148,13 +148,13 @@
     <t>JOSE ALEJANDRO</t>
   </si>
   <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
   </si>
   <si>
     <t>ROSA ITZEL</t>
@@ -1247,13 +1247,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920316</v>
+        <v>21330051920176</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -1262,21 +1262,21 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920176</v>
+        <v>21330051920304</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -1285,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1293,13 +1293,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920304</v>
+        <v>21330051920316</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>TZOPITL</t>
   </si>
   <si>
@@ -140,6 +146,9 @@
   </si>
   <si>
     <t>ANGEL FIDEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -1100,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1138,10 +1147,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,10 +1170,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1184,10 +1193,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1201,16 +1210,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1224,16 +1233,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920202</v>
+        <v>19330061430023</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,45 +1256,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920176</v>
+        <v>21330051920202</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920304</v>
+        <v>21330051920176</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1293,16 +1302,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920316</v>
+        <v>21330051920304</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1316,16 +1325,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920330</v>
+        <v>21330051920316</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1334,6 +1343,29 @@
         <v>14</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920330</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,12 +85,6 @@
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>BERNABE</t>
   </si>
   <si>
@@ -100,27 +94,12 @@
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -130,24 +109,12 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>MARIEL</t>
   </si>
   <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
-  </si>
-  <si>
     <t>IVAN</t>
   </si>
   <si>
@@ -157,16 +124,7 @@
     <t>JOSE ALEJANDRO</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
+    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -960,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -986,16 +944,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>95.12</v>
+        <v>97.56</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1021,7 +979,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1038,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1064,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1090,16 +1048,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7">
-        <v>88.64</v>
+        <v>95.45</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,10 +1105,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1164,22 +1122,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>21330051920188</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1187,22 +1145,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920177</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1210,16 +1168,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920188</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1233,16 +1191,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330061430023</v>
+        <v>21330051920203</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1252,121 +1210,6 @@
       </c>
       <c r="G6">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920202</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920176</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920304</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920316</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920330</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -97,12 +91,6 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>TZOPITL</t>
   </si>
   <si>
@@ -110,12 +98,6 @@
   </si>
   <si>
     <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -1067,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,22 +1081,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920154</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1122,16 +1104,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920188</v>
+        <v>21330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,16 +1127,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330061430023</v>
+        <v>21330051920203</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1163,52 +1145,6 @@
         <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920202</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920203</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -82,31 +82,55 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>TZOPITL</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
     <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1081,22 +1105,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330061430023</v>
+        <v>21330051920165</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1104,22 +1128,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920202</v>
+        <v>21330051920359</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1127,25 +1151,94 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920203</v>
+        <v>21330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330061430023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920203</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
